--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasmindeguzman/Library/Mobile Documents/com~apple~CloudDocs/1 UH MBA/620 Micro and Macro Economoics/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasmindeguzman/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2437257B-B879-2743-A1C3-56EEA5718CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBF9695-0E21-9F44-93CA-6D681CA3393F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32440" yWindow="-5420" windowWidth="24120" windowHeight="19900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32440" yWindow="-5440" windowWidth="29260" windowHeight="19900" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -717,10 +717,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -731,7 +727,6 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -739,15 +734,20 @@
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -831,6 +831,2685 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Tomato Marginal Cost vs. Market Price</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Tomato Price</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:tint val="50000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="35000">
+                    <a:schemeClr val="accent1">
+                      <a:tint val="37000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:tint val="15000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="1"/>
+                <a:tileRect/>
+              </a:gradFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:shade val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Marginal-Cost Schedules'!$J$7:$J$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Marginal-Cost Schedules'!$K$7:$K$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0D3A-614B-89E8-723C07507A6B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Marginal Cost</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:tint val="50000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="35000">
+                    <a:schemeClr val="accent2">
+                      <a:tint val="37000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:tint val="15000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="1"/>
+                <a:tileRect/>
+              </a:gradFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:shade val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Marginal-Cost Schedules'!$A$6:$A$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Marginal-Cost Schedules'!$H$6:$H$26</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0.00</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="1">
+                  <c:v>4317.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5795.6250000000036</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6703.125</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7660.859375</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4906.2750000000051</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5585.7089062500017</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6360.7668437500033</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7243.7792796875074</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8248.586534375012</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9390.7174472031256</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10687.588677253138</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>12158.726978841107</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>13826.017053974152</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15713.977874345364</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17850.070688251115</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>20265.042286194512</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>22993.307496844121</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>26073.375326761772</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>29548.323647694342</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0D3A-614B-89E8-723C07507A6B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="165935551"/>
+        <c:axId val="165935999"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="165935551"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" b="1"/>
+                  <a:t>Tomato Beds</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="165935999"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="165935999"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" b="1"/>
+                  <a:t>Marginal Cost ($)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="165935551"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:alpha val="0"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Carrot Marginal Cost vs. Market Price</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Carrot Price</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:tint val="50000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="35000">
+                    <a:schemeClr val="accent1">
+                      <a:tint val="37000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:tint val="15000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="1"/>
+                <a:tileRect/>
+              </a:gradFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:shade val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Marginal-Cost Schedules'!$J$31:$J$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Marginal-Cost Schedules'!$K$31:$K$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2094</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4CE2-DA48-BC65-CE37A8FC0C9B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Marginal Cost</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:tint val="50000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="35000">
+                    <a:schemeClr val="accent2">
+                      <a:tint val="37000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:tint val="15000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="1"/>
+                <a:tileRect/>
+              </a:gradFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:shade val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Marginal-Cost Schedules'!$A$31:$A$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Marginal-Cost Schedules'!$H$31:$H$51</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0.00</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="1">
+                  <c:v>1507.7083333333333</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1561.0937499999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1616.481119791667</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1673.9371744791652</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1733.530731201171</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1795.332755025227</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1859.4164233334868</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1925.8571920852646</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1994.7328640100477</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2066.1236587860258</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2140.1122852607878</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2216.7840157725441</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2296.2267626316061</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2378.5311568237667</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2463.7906289988823</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2552.1014928097429</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1670.9013431626554</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1589.1387909931072</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1638.1753169880685</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1688.9454575384007</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4CE2-DA48-BC65-CE37A8FC0C9B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="165854079"/>
+        <c:axId val="20858175"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="165854079"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" b="1"/>
+                  <a:t>Carrot Beds</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="20858175"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="20858175"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" b="1"/>
+                  <a:t>Marginal Cost ($)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="165854079"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:alpha val="0"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="246">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="70000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" spc="0" baseline="0"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="95000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1">
+              <a:alpha val="0"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" spc="0" baseline="0"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="246">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="70000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" spc="0" baseline="0"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="95000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1">
+              <a:alpha val="0"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" spc="0" baseline="0"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFAAC1D7-F8C5-B27C-5359-CCD72C7E30E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>615950</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>254000</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BB1E5C2-ADBF-D82E-69D6-8FB6ED4F19FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1022,371 +3701,371 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="6">
         <v>20</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="9">
         <v>8800</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>2.5</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="6">
         <v>880</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="10">
         <v>0.1</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>20</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="9">
         <v>2094</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="11">
         <f>2.5/3</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="6">
         <v>440</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="10">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <v>30</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="9">
         <v>2700</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="6">
         <v>1.25</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="6">
         <v>880</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="10">
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="6">
         <v>36</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="6">
         <v>64</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="9">
         <v>20000</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="9">
         <v>50000</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="6">
         <v>720</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="10">
         <v>0.5</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="9">
         <v>25000</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="6">
         <v>1440</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="6">
         <v>4</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1409,357 +4088,357 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="12">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="12">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="12">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="13">
         <f>OPT_TOM_BEDS*TOM_HRS_PER_BED*WEEKS*(1+TOM_DIM_RET)^OPT_TOM_BEDS</f>
         <v>2334.3682140900019</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="13">
         <f>OPT_CAR_BEDS*CAR_HRS_PER_BED*WEEKS*(1+CAR_DIM_RET)^OPT_CAR_BEDS</f>
         <v>983.16986417423732</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="13">
         <f>OPT_MES_BEDS*MES_HRS_PER_BED*WEEKS*(1+MES_DIM_RET)^OPT_MES_BEDS</f>
         <v>1959.6780360096488</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="13">
         <f>TOM_LABOR_HRS+CAR_LABOR_HRS+MES_LABOR_HRS</f>
         <v>5277.2161142738878</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="13">
         <f>MIN(TOTAL_LABOR_HRS,FARM_AVAIL_HRS)</f>
         <v>720</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="13">
         <f>MAX(TOTAL_LABOR_HRS-FARM_AVAIL_HRS,0)</f>
         <v>4557.2161142738878</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="14">
         <f>ROUNDUP(TEMP_HRS_USED/TEMP_WORK_CAP,0)</f>
         <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="15">
         <f>FARM_SEAS_SAL*FARM_SHARE_FIELD_TIME/FARM_AVAIL_HRS</f>
         <v>34.722222222222221</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="15">
         <f>TEMP_WORK_SEAS_SAL/TEMP_WORK_CAP</f>
         <v>17.361111111111111</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="16">
         <f>FARM_HRS_USED*FARM_RATE+TEMP_HRS_USED*TEMP_RATE</f>
         <v>104118.335317255</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="15">
         <f>IFERROR(TOTAL_LABOR_DOLLARS/TOTAL_LABOR_HRS,0)</f>
         <v>19.729784239010844</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="3" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="17">
         <f>OPT_TOM_BEDS*TOM_PRICE</f>
         <v>88000</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="17">
         <f>OPT_CAR_BEDS*CAR_PRICE</f>
         <v>41880</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="17">
         <f>OPT_MES_BEDS*MES_PRICE</f>
         <v>81000</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="20">
+      <c r="B27" s="17">
         <f>TOM_REVENUE+CAR_REVENUE+MES_REVENUE</f>
         <v>210880</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="20">
+      <c r="B28" s="17">
         <f>OPT_TOM_BEDS*TOM_FERT</f>
         <v>8800</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B29" s="20">
+      <c r="B29" s="17">
         <f>OPT_CAR_BEDS*CAR_FERT</f>
         <v>8800</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B30" s="20">
+      <c r="B30" s="17">
         <f>OPT_MES_BEDS*MES_FERT</f>
         <v>26400</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="20">
+      <c r="B31" s="17">
         <f>TOM_FERT_COST+CAR_FERT_COST+MES_FERT_COST</f>
         <v>44000</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="16">
         <f>TOTAL_FERT_COST+TOTAL_LABOR_DOLLARS+FIX_SEAS_COST</f>
         <v>168118.335317255</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B33" s="19">
+      <c r="B33" s="16">
         <f>TOTAL_REVENUE-TOTAL_COST</f>
         <v>42761.664682745002</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="14">
         <f>TOT_BED_CAP-(OPT_TOM_BEDS+OPT_CAR_BEDS+OPT_MES_BEDS)</f>
         <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="27"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B37" s="19">
+      <c r="B37" s="16">
         <f>IF(OPT_TOM_BEDS&lt;=0,"",TOTAL_COST-((TOTAL_FERT_COST-TOM_FERT)+(MIN((CAR_LABOR_HRS+MES_LABOR_HRS+((OPT_TOM_BEDS-1)*TOM_HRS_PER_BED*WEEKS*(1+TOM_DIM_RET)^(OPT_TOM_BEDS-1))),FARM_AVAIL_HRS)*FARM_RATE+MAX((CAR_LABOR_HRS+MES_LABOR_HRS+((OPT_TOM_BEDS-1)*TOM_HRS_PER_BED*WEEKS*(1+TOM_DIM_RET)^(OPT_TOM_BEDS-1)))-FARM_AVAIL_HRS,0)*TEMP_RATE)+FIX_SEAS_COST))</f>
         <v>8248.5865343750338</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B38" s="19">
+      <c r="B38" s="16">
         <f>IF(OPT_CAR_BEDS&lt;=0,"",TOTAL_COST-((TOTAL_FERT_COST-CAR_FERT)+(MIN((TOM_LABOR_HRS+MES_LABOR_HRS+((OPT_CAR_BEDS-1)*CAR_HRS_PER_BED*WEEKS*(1+CAR_DIM_RET)^(OPT_CAR_BEDS-1))),FARM_AVAIL_HRS)*FARM_RATE+MAX((TOM_LABOR_HRS+MES_LABOR_HRS+((OPT_CAR_BEDS-1)*CAR_HRS_PER_BED*WEEKS*(1+CAR_DIM_RET)^(OPT_CAR_BEDS-1)))-FARM_AVAIL_HRS,0)*TEMP_RATE)+FIX_SEAS_COST))</f>
         <v>1688.9454575384152</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B39" s="19">
+      <c r="B39" s="16">
         <f>IF(OPT_MES_BEDS&lt;=0,"",TOTAL_COST-((TOTAL_FERT_COST-MES_FERT)+(MIN((TOM_LABOR_HRS+CAR_LABOR_HRS+((OPT_MES_BEDS-1)*MES_HRS_PER_BED*WEEKS*(1+MES_DIM_RET)^(OPT_MES_BEDS-1))),FARM_AVAIL_HRS)*FARM_RATE+MAX((TOM_LABOR_HRS+CAR_LABOR_HRS+((OPT_MES_BEDS-1)*MES_HRS_PER_BED*WEEKS*(1+MES_DIM_RET)^(OPT_MES_BEDS-1)))-FARM_AVAIL_HRS,0)*TEMP_RATE)+FIX_SEAS_COST))</f>
         <v>2420.0990509334952</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="27"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="21" t="b">
+      <c r="B42" s="18" t="b">
         <f>OPT_TOM_BEDS&lt;=TOM_MAX_BEDS</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="21" t="b">
+      <c r="B43" s="18" t="b">
         <f>OPT_CAR_BEDS&lt;=CAR_MAX_BEDS</f>
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B44" s="21" t="b">
+      <c r="B44" s="18" t="b">
         <f>OPT_MES_BEDS&lt;=MES_MAX_BEDS</f>
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B45" s="21" t="b">
+      <c r="B45" s="18" t="b">
         <f>(OPT_TOM_BEDS+OPT_CAR_BEDS+OPT_MES_BEDS)&lt;=TOT_BED_CAP</f>
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B46" s="21" t="b">
+      <c r="B46" s="18" t="b">
         <f>REQ_WORKER&lt;=MAX_TEMP_WORK</f>
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B47" s="21" t="b">
-        <f>AND(OPT_TOM_BEDS=ROUND(OPT_TOM_BEDS,0),OPT_TOM_BEDS&gt;=0,OPT_CAR_BEDS=ROUND(OPT_CAR_BEDS,0),OPT_CAR_BEDS&gt;=0,OPT_MES_BEDS=ROUND(OPT_MES_BEDS,0),OPT_MES_BEDS&gt;=0)</f>
+      <c r="B47" s="18" t="b">
+        <f>AND(ABS(OPT_TOM_BEDS-ROUND(OPT_TOM_BEDS,0))&lt;0.000001,OPT_TOM_BEDS&gt;=0,ABS(OPT_CAR_BEDS-ROUND(OPT_CAR_BEDS,0))&lt;0.000001,OPT_CAR_BEDS&gt;=0,ABS(OPT_MES_BEDS-ROUND(OPT_MES_BEDS,0))&lt;0.000001,OPT_MES_BEDS&gt;=0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1776,7 +4455,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1787,2594 +4466,2618 @@
     <col min="7" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+    </row>
+    <row r="2" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+    </row>
+    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="21">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="18">
         <v>0</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="13">
         <f t="shared" ref="B6:B26" si="0">A6*TOM_HRS_PER_BED*WEEKS*(1+TOM_DIM_RET)^A6</f>
         <v>0</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="13">
         <f t="shared" ref="C6:C26" si="1">MIN(B6,FARM_AVAIL_HRS)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="13">
         <f t="shared" ref="D6:D26" si="2">MAX(B6-FARM_AVAIL_HRS,0)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="16">
         <f t="shared" ref="E6:E26" si="3">C6*FARM_RATE+D6*TEMP_RATE</f>
         <v>0</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="17">
         <f t="shared" ref="F6:F26" si="4">A6*TOM_FERT</f>
         <v>0</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="16">
         <f t="shared" ref="G6:G26" si="5">E6+F6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="21"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="21">
+      <c r="H6" s="18"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="18">
         <v>1</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="13">
         <f t="shared" si="0"/>
         <v>99.000000000000014</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="13">
         <f t="shared" si="1"/>
         <v>99.000000000000014</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="16">
         <f t="shared" si="3"/>
         <v>3437.5000000000005</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="17">
         <f t="shared" si="4"/>
         <v>880</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="16">
         <f t="shared" si="5"/>
         <v>4317.5</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="16">
         <f t="shared" ref="H7:H26" si="6">G7-G6</f>
         <v>4317.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="21">
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>8800</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="18">
         <v>2</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="13">
         <f t="shared" si="0"/>
         <v>217.80000000000004</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="13">
         <f t="shared" si="1"/>
         <v>217.80000000000004</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="16">
         <f t="shared" si="3"/>
         <v>7562.5000000000009</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="17">
         <f t="shared" si="4"/>
         <v>1760</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="16">
         <f t="shared" si="5"/>
         <v>9322.5</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="16">
         <f t="shared" si="6"/>
         <v>5005</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="21">
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>8800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="18">
         <v>3</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="13">
         <f t="shared" si="0"/>
         <v>359.37000000000012</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="13">
         <f t="shared" si="1"/>
         <v>359.37000000000012</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="16">
         <f t="shared" si="3"/>
         <v>12478.125000000004</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="17">
         <f t="shared" si="4"/>
         <v>2640</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="16">
         <f t="shared" si="5"/>
         <v>15118.125000000004</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="16">
         <f t="shared" si="6"/>
         <v>5795.6250000000036</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="21">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="18">
         <v>4</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="13">
         <f t="shared" si="0"/>
         <v>527.07600000000014</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="13">
         <f t="shared" si="1"/>
         <v>527.07600000000014</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="16">
         <f t="shared" si="3"/>
         <v>18301.250000000004</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="17">
         <f t="shared" si="4"/>
         <v>3520</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="16">
         <f t="shared" si="5"/>
         <v>21821.250000000004</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="16">
         <f t="shared" si="6"/>
         <v>6703.125</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="21">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="18">
         <v>5</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="13">
         <f t="shared" si="0"/>
         <v>724.72950000000026</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="13">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="13">
         <f t="shared" si="2"/>
         <v>4.7295000000002574</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="16">
         <f t="shared" si="3"/>
         <v>25082.109375000004</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="17">
         <f t="shared" si="4"/>
         <v>4400</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="16">
         <f t="shared" si="5"/>
         <v>29482.109375000004</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="16">
         <f t="shared" si="6"/>
         <v>7660.859375</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="21">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" s="18">
         <v>6</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="13">
         <f t="shared" si="0"/>
         <v>956.64294000000041</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="13">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="13">
         <f t="shared" si="2"/>
         <v>236.64294000000041</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="16">
         <f t="shared" si="3"/>
         <v>29108.384375000009</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="17">
         <f t="shared" si="4"/>
         <v>5280</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="16">
         <f t="shared" si="5"/>
         <v>34388.384375000009</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="16">
         <f t="shared" si="6"/>
         <v>4906.2750000000051</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="21">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="18">
         <v>7</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="13">
         <f t="shared" si="0"/>
         <v>1227.6917730000007</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="13">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="13">
         <f t="shared" si="2"/>
         <v>507.69177300000069</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="16">
         <f t="shared" si="3"/>
         <v>33814.09328125001</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="17">
         <f t="shared" si="4"/>
         <v>6160</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="16">
         <f t="shared" si="5"/>
         <v>39974.09328125001</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="16">
         <f t="shared" si="6"/>
         <v>5585.7089062500017</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="21">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" s="18">
         <v>8</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="13">
         <f t="shared" si="0"/>
         <v>1543.3839432000009</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="13">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="13">
         <f t="shared" si="2"/>
         <v>823.38394320000089</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="16">
         <f t="shared" si="3"/>
         <v>39294.860125000014</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="17">
         <f t="shared" si="4"/>
         <v>7040</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="16">
         <f t="shared" si="5"/>
         <v>46334.860125000014</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="16">
         <f t="shared" si="6"/>
         <v>6360.7668437500033</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="21">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="18">
         <v>9</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="13">
         <f t="shared" si="0"/>
         <v>1909.9376297100011</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="13">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="13">
         <f t="shared" si="2"/>
         <v>1189.9376297100011</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="16">
         <f t="shared" si="3"/>
         <v>45658.639404687521</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="17">
         <f t="shared" si="4"/>
         <v>7920</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="16">
         <f t="shared" si="5"/>
         <v>53578.639404687521</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="16">
         <f t="shared" si="6"/>
         <v>7243.7792796875074</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="21">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="18">
         <v>10</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="13">
         <f t="shared" si="0"/>
         <v>2334.3682140900019</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="13">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="13">
         <f t="shared" si="2"/>
         <v>1614.3682140900019</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="16">
         <f t="shared" si="3"/>
         <v>53027.225939062533</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="17">
         <f t="shared" si="4"/>
         <v>8800</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="16">
         <f t="shared" si="5"/>
         <v>61827.225939062533</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="16">
         <f t="shared" si="6"/>
         <v>8248.586534375012</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="21">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="18">
         <v>11</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="13">
         <f t="shared" si="0"/>
         <v>2824.5855390489023</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="13">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="13">
         <f t="shared" si="2"/>
         <v>2104.5855390489023</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="16">
         <f t="shared" si="3"/>
         <v>61537.943386265666</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="17">
         <f t="shared" si="4"/>
         <v>9680</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="16">
         <f t="shared" si="5"/>
         <v>71217.943386265659</v>
       </c>
-      <c r="H17" s="19">
+      <c r="H17" s="16">
         <f t="shared" si="6"/>
         <v>9390.7174472031256</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="21">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="18">
         <v>12</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="13">
         <f t="shared" si="0"/>
         <v>3389.502646858683</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="13">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="13">
         <f t="shared" si="2"/>
         <v>2669.502646858683</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="16">
         <f t="shared" si="3"/>
         <v>71345.532063518796</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="17">
         <f t="shared" si="4"/>
         <v>10560</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="16">
         <f t="shared" si="5"/>
         <v>81905.532063518796</v>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="16">
         <f t="shared" si="6"/>
         <v>10687.588677253138</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="21">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="18">
         <v>13</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="13">
         <f t="shared" si="0"/>
         <v>4039.1573208399304</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="13">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="13">
         <f t="shared" si="2"/>
         <v>3319.1573208399304</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="16">
         <f t="shared" si="3"/>
         <v>82624.259042359903</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="17">
         <f t="shared" si="4"/>
         <v>11440</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="16">
         <f t="shared" si="5"/>
         <v>94064.259042359903</v>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="16">
         <f t="shared" si="6"/>
         <v>12158.726978841107</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="21">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="18">
         <v>14</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="13">
         <f t="shared" si="0"/>
         <v>4784.8479031488414</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="13">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="13">
         <f t="shared" si="2"/>
         <v>4064.8479031488414</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="16">
         <f t="shared" si="3"/>
         <v>95570.276096334055</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="17">
         <f t="shared" si="4"/>
         <v>12320</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="16">
         <f t="shared" si="5"/>
         <v>107890.27609633406</v>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="16">
         <f t="shared" si="6"/>
         <v>13826.017053974152</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="21">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="18">
         <v>15</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="13">
         <f t="shared" si="0"/>
         <v>5639.2850287111351</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="13">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="13">
         <f t="shared" si="2"/>
         <v>4919.2850287111351</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="16">
         <f t="shared" si="3"/>
         <v>110404.25397067942</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="17">
         <f t="shared" si="4"/>
         <v>13200</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="16">
         <f t="shared" si="5"/>
         <v>123604.25397067942</v>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="16">
         <f t="shared" si="6"/>
         <v>15713.977874345364</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="21">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="18">
         <v>16</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="13">
         <f t="shared" si="0"/>
         <v>6616.761100354398</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="13">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="13">
         <f t="shared" si="2"/>
         <v>5896.761100354398</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="16">
         <f t="shared" si="3"/>
         <v>127374.32465893052</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="17">
         <f t="shared" si="4"/>
         <v>14080</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="16">
         <f t="shared" si="5"/>
         <v>141454.32465893053</v>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="16">
         <f t="shared" si="6"/>
         <v>17850.070688251115</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="21">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" s="18">
         <v>17</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="13">
         <f t="shared" si="0"/>
         <v>7733.3395360392033</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="13">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="13">
         <f t="shared" si="2"/>
         <v>7013.3395360392033</v>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="16">
         <f t="shared" si="3"/>
         <v>146759.36694512505</v>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="17">
         <f t="shared" si="4"/>
         <v>14960</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="16">
         <f t="shared" si="5"/>
         <v>161719.36694512505</v>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="16">
         <f t="shared" si="6"/>
         <v>20265.042286194512</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="21">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="18">
         <v>18</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="13">
         <f t="shared" si="0"/>
         <v>9007.0660478574246</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="13">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="13">
         <f t="shared" si="2"/>
         <v>8287.0660478574246</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="16">
         <f t="shared" si="3"/>
         <v>168872.67444196917</v>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="17">
         <f t="shared" si="4"/>
         <v>15840</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="16">
         <f t="shared" si="5"/>
         <v>184712.67444196917</v>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="16">
         <f t="shared" si="6"/>
         <v>22993.307496844121</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="21">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="18">
         <v>19</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="13">
         <f t="shared" si="0"/>
         <v>10458.204466678902</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="13">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="13">
         <f t="shared" si="2"/>
         <v>9738.2044666789025</v>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="16">
         <f t="shared" si="3"/>
         <v>194066.04976873094</v>
       </c>
-      <c r="F25" s="20">
+      <c r="F25" s="17">
         <f t="shared" si="4"/>
         <v>16720</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="16">
         <f t="shared" si="5"/>
         <v>210786.04976873094</v>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="16">
         <f t="shared" si="6"/>
         <v>26073.375326761772</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="21">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="18">
         <v>20</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="13">
         <f t="shared" si="0"/>
         <v>12109.499908786096</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="13">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="13">
         <f t="shared" si="2"/>
         <v>11389.499908786096</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="16">
         <f t="shared" si="3"/>
         <v>222734.37341642528</v>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="17">
         <f t="shared" si="4"/>
         <v>17600</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="16">
         <f t="shared" si="5"/>
         <v>240334.37341642528</v>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="16">
         <f t="shared" si="6"/>
         <v>29548.323647694342</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="23" t="s">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="20">
         <f>TOM_PRICE</f>
         <v>8800</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-    </row>
-    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+    </row>
+    <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H30" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="21">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" s="18">
         <v>0</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="13">
         <f t="shared" ref="B31:B51" si="7">A31*CAR_HRS_PER_BED*WEEKS*(1+CAR_DIM_RET)^A31</f>
         <v>0</v>
       </c>
-      <c r="C31" s="16">
+      <c r="C31" s="13">
         <f t="shared" ref="C31:C51" si="8">MIN(B31,FARM_AVAIL_HRS)</f>
         <v>0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="13">
         <f t="shared" ref="D31:D51" si="9">MAX(B31-FARM_AVAIL_HRS,0)</f>
         <v>0</v>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="16">
         <f t="shared" ref="E31:E51" si="10">C31*FARM_RATE+D31*TEMP_RATE</f>
         <v>0</v>
       </c>
-      <c r="F31" s="20">
+      <c r="F31" s="17">
         <f t="shared" ref="F31:F51" si="11">A31*CAR_FERT</f>
         <v>0</v>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="16">
         <f t="shared" ref="G31:G51" si="12">E31+F31</f>
         <v>0</v>
       </c>
-      <c r="H31" s="21"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="21">
+      <c r="H31" s="18"/>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="18">
         <v>1</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="13">
         <f t="shared" si="7"/>
         <v>30.749999999999996</v>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="13">
         <f t="shared" si="8"/>
         <v>30.749999999999996</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="16">
         <f t="shared" si="10"/>
         <v>1067.7083333333333</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="17">
         <f t="shared" si="11"/>
         <v>440</v>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="16">
         <f t="shared" si="12"/>
         <v>1507.7083333333333</v>
       </c>
-      <c r="H32" s="19">
+      <c r="H32" s="16">
         <f t="shared" ref="H32:H51" si="13">G32-G31</f>
         <v>1507.7083333333333</v>
       </c>
+      <c r="J32">
+        <v>20</v>
+      </c>
+      <c r="K32">
+        <v>2094</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="21">
+      <c r="A33" s="18">
         <v>2</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="13">
         <f t="shared" si="7"/>
         <v>63.037499999999994</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="13">
         <f t="shared" si="8"/>
         <v>63.037499999999994</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E33" s="19">
+      <c r="E33" s="16">
         <f t="shared" si="10"/>
         <v>2188.802083333333</v>
       </c>
-      <c r="F33" s="20">
+      <c r="F33" s="17">
         <f t="shared" si="11"/>
         <v>880</v>
       </c>
-      <c r="G33" s="19">
+      <c r="G33" s="16">
         <f t="shared" si="12"/>
         <v>3068.802083333333</v>
       </c>
-      <c r="H33" s="19">
+      <c r="H33" s="16">
         <f t="shared" si="13"/>
         <v>1561.0937499999998</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="21">
+      <c r="A34" s="18">
         <v>3</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="13">
         <f t="shared" si="7"/>
         <v>96.920156249999991</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="13">
         <f t="shared" si="8"/>
         <v>96.920156249999991</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="16">
         <f t="shared" si="10"/>
         <v>3365.2832031249995</v>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="17">
         <f t="shared" si="11"/>
         <v>1320</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="16">
         <f t="shared" si="12"/>
         <v>4685.283203125</v>
       </c>
-      <c r="H34" s="19">
+      <c r="H34" s="16">
         <f t="shared" si="13"/>
         <v>1616.481119791667</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="21">
+      <c r="A35" s="18">
         <v>4</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="13">
         <f t="shared" si="7"/>
         <v>132.45754687499996</v>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="13">
         <f t="shared" si="8"/>
         <v>132.45754687499996</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E35" s="19">
+      <c r="E35" s="16">
         <f t="shared" si="10"/>
         <v>4599.2203776041652</v>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="17">
         <f t="shared" si="11"/>
         <v>1760</v>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="16">
         <f t="shared" si="12"/>
         <v>6359.2203776041652</v>
       </c>
-      <c r="H35" s="19">
+      <c r="H35" s="16">
         <f t="shared" si="13"/>
         <v>1673.9371744791652</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="21">
+      <c r="A36" s="18">
         <v>5</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="13">
         <f t="shared" si="7"/>
         <v>169.71123193359369</v>
       </c>
-      <c r="C36" s="16">
+      <c r="C36" s="13">
         <f t="shared" si="8"/>
         <v>169.71123193359369</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E36" s="19">
+      <c r="E36" s="16">
         <f t="shared" si="10"/>
         <v>5892.7511088053361</v>
       </c>
-      <c r="F36" s="20">
+      <c r="F36" s="17">
         <f t="shared" si="11"/>
         <v>2200</v>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="16">
         <f t="shared" si="12"/>
         <v>8092.7511088053361</v>
       </c>
-      <c r="H36" s="19">
+      <c r="H36" s="16">
         <f t="shared" si="13"/>
         <v>1733.530731201171</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="21">
+      <c r="A37" s="18">
         <v>6</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="13">
         <f t="shared" si="7"/>
         <v>208.74481527832023</v>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="13">
         <f t="shared" si="8"/>
         <v>208.74481527832023</v>
       </c>
-      <c r="D37" s="16">
+      <c r="D37" s="13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E37" s="19">
+      <c r="E37" s="16">
         <f t="shared" si="10"/>
         <v>7248.0838638305631</v>
       </c>
-      <c r="F37" s="20">
+      <c r="F37" s="17">
         <f t="shared" si="11"/>
         <v>2640</v>
       </c>
-      <c r="G37" s="19">
+      <c r="G37" s="16">
         <f t="shared" si="12"/>
         <v>9888.0838638305631</v>
       </c>
-      <c r="H37" s="19">
+      <c r="H37" s="16">
         <f t="shared" si="13"/>
         <v>1795.332755025227</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="21">
+      <c r="A38" s="18">
         <v>7</v>
       </c>
-      <c r="B38" s="16">
+      <c r="B38" s="13">
         <f t="shared" si="7"/>
         <v>249.62400827032465</v>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="13">
         <f t="shared" si="8"/>
         <v>249.62400827032465</v>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E38" s="19">
+      <c r="E38" s="16">
         <f t="shared" si="10"/>
         <v>8667.50028716405</v>
       </c>
-      <c r="F38" s="20">
+      <c r="F38" s="17">
         <f t="shared" si="11"/>
         <v>3080</v>
       </c>
-      <c r="G38" s="19">
+      <c r="G38" s="16">
         <f t="shared" si="12"/>
         <v>11747.50028716405</v>
       </c>
-      <c r="H38" s="19">
+      <c r="H38" s="16">
         <f t="shared" si="13"/>
         <v>1859.4164233334868</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="21">
+      <c r="A39" s="18">
         <v>8</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="13">
         <f t="shared" si="7"/>
         <v>292.41669540238024</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="13">
         <f t="shared" si="8"/>
         <v>292.41669540238024</v>
       </c>
-      <c r="D39" s="16">
+      <c r="D39" s="13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E39" s="19">
+      <c r="E39" s="16">
         <f t="shared" si="10"/>
         <v>10153.357479249315</v>
       </c>
-      <c r="F39" s="20">
+      <c r="F39" s="17">
         <f t="shared" si="11"/>
         <v>3520</v>
       </c>
-      <c r="G39" s="19">
+      <c r="G39" s="16">
         <f t="shared" si="12"/>
         <v>13673.357479249315</v>
       </c>
-      <c r="H39" s="19">
+      <c r="H39" s="16">
         <f t="shared" si="13"/>
         <v>1925.8571920852646</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="21">
+      <c r="A40" s="18">
         <v>9</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="13">
         <f t="shared" si="7"/>
         <v>337.19300188586965</v>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="13">
         <f t="shared" si="8"/>
         <v>337.19300188586965</v>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E40" s="19">
+      <c r="E40" s="16">
         <f t="shared" si="10"/>
         <v>11708.090343259362</v>
       </c>
-      <c r="F40" s="20">
+      <c r="F40" s="17">
         <f t="shared" si="11"/>
         <v>3960</v>
       </c>
-      <c r="G40" s="19">
+      <c r="G40" s="16">
         <f t="shared" si="12"/>
         <v>15668.090343259362</v>
       </c>
-      <c r="H40" s="19">
+      <c r="H40" s="16">
         <f t="shared" si="13"/>
         <v>1994.7328640100477</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="21">
+      <c r="A41" s="18">
         <v>10</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="13">
         <f t="shared" si="7"/>
         <v>384.02536325890713</v>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="13">
         <f t="shared" si="8"/>
         <v>384.02536325890713</v>
       </c>
-      <c r="D41" s="16">
+      <c r="D41" s="13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E41" s="19">
+      <c r="E41" s="16">
         <f t="shared" si="10"/>
         <v>13334.214002045386</v>
       </c>
-      <c r="F41" s="20">
+      <c r="F41" s="17">
         <f t="shared" si="11"/>
         <v>4400</v>
       </c>
-      <c r="G41" s="19">
+      <c r="G41" s="16">
         <f t="shared" si="12"/>
         <v>17734.214002045388</v>
       </c>
-      <c r="H41" s="19">
+      <c r="H41" s="16">
         <f t="shared" si="13"/>
         <v>2066.1236587860258</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="21">
+      <c r="A42" s="18">
         <v>11</v>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="13">
         <f t="shared" si="7"/>
         <v>432.98859707441784</v>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="13">
         <f t="shared" si="8"/>
         <v>432.98859707441784</v>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E42" s="19">
+      <c r="E42" s="16">
         <f t="shared" si="10"/>
         <v>15034.326287306174</v>
       </c>
-      <c r="F42" s="20">
+      <c r="F42" s="17">
         <f t="shared" si="11"/>
         <v>4840</v>
       </c>
-      <c r="G42" s="19">
+      <c r="G42" s="16">
         <f t="shared" si="12"/>
         <v>19874.326287306176</v>
       </c>
-      <c r="H42" s="19">
+      <c r="H42" s="16">
         <f t="shared" si="13"/>
         <v>2140.1122852607878</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="21">
+      <c r="A43" s="18">
         <v>12</v>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="13">
         <f t="shared" si="7"/>
         <v>484.15997672866712</v>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="13">
         <f t="shared" si="8"/>
         <v>484.15997672866712</v>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E43" s="19">
+      <c r="E43" s="16">
         <f t="shared" si="10"/>
         <v>16811.11030307872</v>
       </c>
-      <c r="F43" s="20">
+      <c r="F43" s="17">
         <f t="shared" si="11"/>
         <v>5280</v>
       </c>
-      <c r="G43" s="19">
+      <c r="G43" s="16">
         <f t="shared" si="12"/>
         <v>22091.11030307872</v>
       </c>
-      <c r="H43" s="19">
+      <c r="H43" s="16">
         <f t="shared" si="13"/>
         <v>2216.7840157725441</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="21">
+      <c r="A44" s="18">
         <v>13</v>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="13">
         <f t="shared" si="7"/>
         <v>537.61930749245744</v>
       </c>
-      <c r="C44" s="16">
+      <c r="C44" s="13">
         <f t="shared" si="8"/>
         <v>537.61930749245744</v>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E44" s="19">
+      <c r="E44" s="16">
         <f t="shared" si="10"/>
         <v>18667.337065710326</v>
       </c>
-      <c r="F44" s="20">
+      <c r="F44" s="17">
         <f t="shared" si="11"/>
         <v>5720</v>
       </c>
-      <c r="G44" s="19">
+      <c r="G44" s="16">
         <f t="shared" si="12"/>
         <v>24387.337065710326</v>
       </c>
-      <c r="H44" s="19">
+      <c r="H44" s="16">
         <f t="shared" si="13"/>
         <v>2296.2267626316061</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="21">
+      <c r="A45" s="18">
         <v>14</v>
       </c>
-      <c r="B45" s="16">
+      <c r="B45" s="13">
         <f t="shared" si="7"/>
         <v>593.44900480898184</v>
       </c>
-      <c r="C45" s="16">
+      <c r="C45" s="13">
         <f t="shared" si="8"/>
         <v>593.44900480898184</v>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E45" s="19">
+      <c r="E45" s="16">
         <f t="shared" si="10"/>
         <v>20605.868222534093</v>
       </c>
-      <c r="F45" s="20">
+      <c r="F45" s="17">
         <f t="shared" si="11"/>
         <v>6160</v>
       </c>
-      <c r="G45" s="19">
+      <c r="G45" s="16">
         <f t="shared" si="12"/>
         <v>26765.868222534093</v>
       </c>
-      <c r="H45" s="19">
+      <c r="H45" s="16">
         <f t="shared" si="13"/>
         <v>2378.5311568237667</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="21">
+      <c r="A46" s="18">
         <v>15</v>
       </c>
-      <c r="B46" s="16">
+      <c r="B46" s="13">
         <f t="shared" si="7"/>
         <v>651.73417492414967</v>
       </c>
-      <c r="C46" s="16">
+      <c r="C46" s="13">
         <f t="shared" si="8"/>
         <v>651.73417492414967</v>
       </c>
-      <c r="D46" s="16">
+      <c r="D46" s="13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E46" s="19">
+      <c r="E46" s="16">
         <f t="shared" si="10"/>
         <v>22629.658851532975</v>
       </c>
-      <c r="F46" s="20">
+      <c r="F46" s="17">
         <f t="shared" si="11"/>
         <v>6600</v>
       </c>
-      <c r="G46" s="19">
+      <c r="G46" s="16">
         <f t="shared" si="12"/>
         <v>29229.658851532975</v>
       </c>
-      <c r="H46" s="19">
+      <c r="H46" s="16">
         <f t="shared" si="13"/>
         <v>2463.7906289988823</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="21">
+      <c r="A47" s="18">
         <v>16</v>
       </c>
-      <c r="B47" s="16">
+      <c r="B47" s="13">
         <f t="shared" si="7"/>
         <v>712.5626979170703</v>
       </c>
-      <c r="C47" s="16">
+      <c r="C47" s="13">
         <f t="shared" si="8"/>
         <v>712.5626979170703</v>
       </c>
-      <c r="D47" s="16">
+      <c r="D47" s="13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E47" s="19">
+      <c r="E47" s="16">
         <f t="shared" si="10"/>
         <v>24741.760344342718</v>
       </c>
-      <c r="F47" s="20">
+      <c r="F47" s="17">
         <f t="shared" si="11"/>
         <v>7040</v>
       </c>
-      <c r="G47" s="19">
+      <c r="G47" s="16">
         <f t="shared" si="12"/>
         <v>31781.760344342718</v>
       </c>
-      <c r="H47" s="19">
+      <c r="H47" s="16">
         <f t="shared" si="13"/>
         <v>2552.1014928097429</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="21">
+      <c r="A48" s="18">
         <v>17</v>
       </c>
-      <c r="B48" s="16">
+      <c r="B48" s="13">
         <f t="shared" si="7"/>
         <v>776.02531320030937</v>
       </c>
-      <c r="C48" s="16">
+      <c r="C48" s="13">
         <f t="shared" si="8"/>
         <v>720</v>
       </c>
-      <c r="D48" s="16">
+      <c r="D48" s="13">
         <f t="shared" si="9"/>
         <v>56.02531320030937</v>
       </c>
-      <c r="E48" s="19">
+      <c r="E48" s="16">
         <f t="shared" si="10"/>
         <v>25972.66168750537</v>
       </c>
-      <c r="F48" s="20">
+      <c r="F48" s="17">
         <f t="shared" si="11"/>
         <v>7480</v>
       </c>
-      <c r="G48" s="19">
+      <c r="G48" s="16">
         <f t="shared" si="12"/>
         <v>33452.661687505373</v>
       </c>
-      <c r="H48" s="19">
+      <c r="H48" s="16">
         <f t="shared" si="13"/>
         <v>1670.9013431626554</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="21">
+      <c r="A49" s="18">
         <v>18</v>
       </c>
-      <c r="B49" s="16">
+      <c r="B49" s="13">
         <f t="shared" si="7"/>
         <v>842.2157075615122</v>
       </c>
-      <c r="C49" s="16">
+      <c r="C49" s="13">
         <f t="shared" si="8"/>
         <v>720</v>
       </c>
-      <c r="D49" s="16">
+      <c r="D49" s="13">
         <f t="shared" si="9"/>
         <v>122.2157075615122</v>
       </c>
-      <c r="E49" s="19">
+      <c r="E49" s="16">
         <f t="shared" si="10"/>
         <v>27121.800478498477</v>
       </c>
-      <c r="F49" s="20">
+      <c r="F49" s="17">
         <f t="shared" si="11"/>
         <v>7920</v>
       </c>
-      <c r="G49" s="19">
+      <c r="G49" s="16">
         <f t="shared" si="12"/>
         <v>35041.800478498481</v>
       </c>
-      <c r="H49" s="19">
+      <c r="H49" s="16">
         <f t="shared" si="13"/>
         <v>1589.1387909931072</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="21">
+      <c r="A50" s="18">
         <v>19</v>
       </c>
-      <c r="B50" s="16">
+      <c r="B50" s="13">
         <f t="shared" si="7"/>
         <v>911.23060582002495</v>
       </c>
-      <c r="C50" s="16">
+      <c r="C50" s="13">
         <f t="shared" si="8"/>
         <v>720</v>
       </c>
-      <c r="D50" s="16">
+      <c r="D50" s="13">
         <f t="shared" si="9"/>
         <v>191.23060582002495</v>
       </c>
-      <c r="E50" s="19">
+      <c r="E50" s="16">
         <f t="shared" si="10"/>
         <v>28319.975795486545</v>
       </c>
-      <c r="F50" s="20">
+      <c r="F50" s="17">
         <f t="shared" si="11"/>
         <v>8360</v>
       </c>
-      <c r="G50" s="19">
+      <c r="G50" s="16">
         <f t="shared" si="12"/>
         <v>36679.975795486549</v>
       </c>
-      <c r="H50" s="19">
+      <c r="H50" s="16">
         <f t="shared" si="13"/>
         <v>1638.1753169880685</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="21">
+      <c r="A51" s="18">
         <v>20</v>
       </c>
-      <c r="B51" s="16">
+      <c r="B51" s="13">
         <f t="shared" si="7"/>
         <v>983.16986417423732</v>
       </c>
-      <c r="C51" s="16">
+      <c r="C51" s="13">
         <f t="shared" si="8"/>
         <v>720</v>
       </c>
-      <c r="D51" s="16">
+      <c r="D51" s="13">
         <f t="shared" si="9"/>
         <v>263.16986417423732</v>
       </c>
-      <c r="E51" s="19">
+      <c r="E51" s="16">
         <f t="shared" si="10"/>
         <v>29568.921253024953</v>
       </c>
-      <c r="F51" s="20">
+      <c r="F51" s="17">
         <f t="shared" si="11"/>
         <v>8800</v>
       </c>
-      <c r="G51" s="19">
+      <c r="G51" s="16">
         <f t="shared" si="12"/>
         <v>38368.92125302495</v>
       </c>
-      <c r="H51" s="19">
+      <c r="H51" s="16">
         <f t="shared" si="13"/>
         <v>1688.9454575384007</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="23" t="s">
+      <c r="A52" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B52" s="24">
+      <c r="B52" s="20">
         <f>CAR_PRICE</f>
         <v>2094</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
     </row>
     <row r="55" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E55" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F55" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G55" s="6" t="s">
+      <c r="G55" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H55" s="6" t="s">
+      <c r="H55" s="4" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="21">
+      <c r="A56" s="18">
         <v>0</v>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="13">
         <f t="shared" ref="B56:B86" si="14">A56*MES_HRS_PER_BED*WEEKS*(1+MES_DIM_RET)^A56</f>
         <v>0</v>
       </c>
-      <c r="C56" s="16">
+      <c r="C56" s="13">
         <f t="shared" ref="C56:C86" si="15">MIN(B56,FARM_AVAIL_HRS)</f>
         <v>0</v>
       </c>
-      <c r="D56" s="16">
+      <c r="D56" s="13">
         <f t="shared" ref="D56:D86" si="16">MAX(B56-FARM_AVAIL_HRS,0)</f>
         <v>0</v>
       </c>
-      <c r="E56" s="19">
+      <c r="E56" s="16">
         <f t="shared" ref="E56:E86" si="17">C56*FARM_RATE+D56*TEMP_RATE</f>
         <v>0</v>
       </c>
-      <c r="F56" s="20">
+      <c r="F56" s="17">
         <f t="shared" ref="F56:F86" si="18">A56*MES_FERT</f>
         <v>0</v>
       </c>
-      <c r="G56" s="19">
+      <c r="G56" s="16">
         <f t="shared" ref="G56:G86" si="19">E56+F56</f>
         <v>0</v>
       </c>
-      <c r="H56" s="21"/>
+      <c r="H56" s="18"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="21">
+      <c r="A57" s="18">
         <v>1</v>
       </c>
-      <c r="B57" s="16">
+      <c r="B57" s="13">
         <f t="shared" si="14"/>
         <v>45.5625</v>
       </c>
-      <c r="C57" s="16">
+      <c r="C57" s="13">
         <f t="shared" si="15"/>
         <v>45.5625</v>
       </c>
-      <c r="D57" s="16">
+      <c r="D57" s="13">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E57" s="19">
+      <c r="E57" s="16">
         <f t="shared" si="17"/>
         <v>1582.03125</v>
       </c>
-      <c r="F57" s="20">
+      <c r="F57" s="17">
         <f t="shared" si="18"/>
         <v>880</v>
       </c>
-      <c r="G57" s="19">
+      <c r="G57" s="16">
         <f t="shared" si="19"/>
         <v>2462.03125</v>
       </c>
-      <c r="H57" s="19">
+      <c r="H57" s="16">
         <f t="shared" ref="H57:H86" si="20">G57-G56</f>
         <v>2462.03125</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="21">
+      <c r="A58" s="18">
         <v>2</v>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="13">
         <f t="shared" si="14"/>
         <v>92.264062499999994</v>
       </c>
-      <c r="C58" s="16">
+      <c r="C58" s="13">
         <f t="shared" si="15"/>
         <v>92.264062499999994</v>
       </c>
-      <c r="D58" s="16">
+      <c r="D58" s="13">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E58" s="19">
+      <c r="E58" s="16">
         <f t="shared" si="17"/>
         <v>3203.6132812499995</v>
       </c>
-      <c r="F58" s="20">
+      <c r="F58" s="17">
         <f t="shared" si="18"/>
         <v>1760</v>
       </c>
-      <c r="G58" s="19">
+      <c r="G58" s="16">
         <f t="shared" si="19"/>
         <v>4963.61328125</v>
       </c>
-      <c r="H58" s="19">
+      <c r="H58" s="16">
         <f t="shared" si="20"/>
         <v>2501.58203125</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="21">
+      <c r="A59" s="18">
         <v>3</v>
       </c>
-      <c r="B59" s="16">
+      <c r="B59" s="13">
         <f t="shared" si="14"/>
         <v>140.12604492187498</v>
       </c>
-      <c r="C59" s="16">
+      <c r="C59" s="13">
         <f t="shared" si="15"/>
         <v>140.12604492187498</v>
       </c>
-      <c r="D59" s="16">
+      <c r="D59" s="13">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E59" s="19">
+      <c r="E59" s="16">
         <f t="shared" si="17"/>
         <v>4865.4876708984366</v>
       </c>
-      <c r="F59" s="20">
+      <c r="F59" s="17">
         <f t="shared" si="18"/>
         <v>2640</v>
       </c>
-      <c r="G59" s="19">
+      <c r="G59" s="16">
         <f t="shared" si="19"/>
         <v>7505.4876708984366</v>
       </c>
-      <c r="H59" s="19">
+      <c r="H59" s="16">
         <f t="shared" si="20"/>
         <v>2541.8743896484366</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="21">
+      <c r="A60" s="18">
         <v>4</v>
       </c>
-      <c r="B60" s="16">
+      <c r="B60" s="13">
         <f t="shared" si="14"/>
         <v>189.17016064453125</v>
       </c>
-      <c r="C60" s="16">
+      <c r="C60" s="13">
         <f t="shared" si="15"/>
         <v>189.17016064453125</v>
       </c>
-      <c r="D60" s="16">
+      <c r="D60" s="13">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E60" s="19">
+      <c r="E60" s="16">
         <f t="shared" si="17"/>
         <v>6568.4083557128906</v>
       </c>
-      <c r="F60" s="20">
+      <c r="F60" s="17">
         <f t="shared" si="18"/>
         <v>3520</v>
       </c>
-      <c r="G60" s="19">
+      <c r="G60" s="16">
         <f t="shared" si="19"/>
         <v>10088.408355712891</v>
       </c>
-      <c r="H60" s="19">
+      <c r="H60" s="16">
         <f t="shared" si="20"/>
         <v>2582.920684814454</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="21">
+      <c r="A61" s="18">
         <v>5</v>
       </c>
-      <c r="B61" s="16">
+      <c r="B61" s="13">
         <f t="shared" si="14"/>
         <v>239.41848456573481</v>
       </c>
-      <c r="C61" s="16">
+      <c r="C61" s="13">
         <f t="shared" si="15"/>
         <v>239.41848456573481</v>
       </c>
-      <c r="D61" s="16">
+      <c r="D61" s="13">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E61" s="19">
+      <c r="E61" s="16">
         <f t="shared" si="17"/>
         <v>8313.1418251991254</v>
       </c>
-      <c r="F61" s="20">
+      <c r="F61" s="17">
         <f t="shared" si="18"/>
         <v>4400</v>
       </c>
-      <c r="G61" s="19">
+      <c r="G61" s="16">
         <f t="shared" si="19"/>
         <v>12713.141825199125</v>
       </c>
-      <c r="H61" s="19">
+      <c r="H61" s="16">
         <f t="shared" si="20"/>
         <v>2624.7334694862348</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" s="21">
+      <c r="A62" s="18">
         <v>6</v>
       </c>
-      <c r="B62" s="16">
+      <c r="B62" s="13">
         <f t="shared" si="14"/>
         <v>290.89345874736784</v>
       </c>
-      <c r="C62" s="16">
+      <c r="C62" s="13">
         <f t="shared" si="15"/>
         <v>290.89345874736784</v>
       </c>
-      <c r="D62" s="16">
+      <c r="D62" s="13">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E62" s="19">
+      <c r="E62" s="16">
         <f t="shared" si="17"/>
         <v>10100.467317616938</v>
       </c>
-      <c r="F62" s="20">
+      <c r="F62" s="17">
         <f t="shared" si="18"/>
         <v>5280</v>
       </c>
-      <c r="G62" s="19">
+      <c r="G62" s="16">
         <f t="shared" si="19"/>
         <v>15380.467317616938</v>
       </c>
-      <c r="H62" s="19">
+      <c r="H62" s="16">
         <f t="shared" si="20"/>
         <v>2667.3254924178127</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="21">
+      <c r="A63" s="18">
         <v>7</v>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="13">
         <f t="shared" si="14"/>
         <v>343.61789814532818</v>
       </c>
-      <c r="C63" s="16">
+      <c r="C63" s="13">
         <f t="shared" si="15"/>
         <v>343.61789814532818</v>
       </c>
-      <c r="D63" s="16">
+      <c r="D63" s="13">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E63" s="19">
+      <c r="E63" s="16">
         <f t="shared" si="17"/>
         <v>11931.177018935006</v>
       </c>
-      <c r="F63" s="20">
+      <c r="F63" s="17">
         <f t="shared" si="18"/>
         <v>6160</v>
       </c>
-      <c r="G63" s="19">
+      <c r="G63" s="16">
         <f t="shared" si="19"/>
         <v>18091.177018935006</v>
       </c>
-      <c r="H63" s="19">
+      <c r="H63" s="16">
         <f t="shared" si="20"/>
         <v>2710.7097013180683</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="21">
+      <c r="A64" s="18">
         <v>8</v>
       </c>
-      <c r="B64" s="16">
+      <c r="B64" s="13">
         <f t="shared" si="14"/>
         <v>397.61499642530839</v>
       </c>
-      <c r="C64" s="16">
+      <c r="C64" s="13">
         <f t="shared" si="15"/>
         <v>397.61499642530839</v>
       </c>
-      <c r="D64" s="16">
+      <c r="D64" s="13">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E64" s="19">
+      <c r="E64" s="16">
         <f t="shared" si="17"/>
         <v>13806.076264767653</v>
       </c>
-      <c r="F64" s="20">
+      <c r="F64" s="17">
         <f t="shared" si="18"/>
         <v>7040</v>
       </c>
-      <c r="G64" s="19">
+      <c r="G64" s="16">
         <f t="shared" si="19"/>
         <v>20846.076264767653</v>
       </c>
-      <c r="H64" s="19">
+      <c r="H64" s="16">
         <f t="shared" si="20"/>
         <v>2754.8992458326466</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65" s="21">
+      <c r="A65" s="18">
         <v>9</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B65" s="13">
         <f t="shared" si="14"/>
         <v>452.90833186570285</v>
       </c>
-      <c r="C65" s="16">
+      <c r="C65" s="13">
         <f t="shared" si="15"/>
         <v>452.90833186570285</v>
       </c>
-      <c r="D65" s="16">
+      <c r="D65" s="13">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E65" s="19">
+      <c r="E65" s="16">
         <f t="shared" si="17"/>
         <v>15725.983745336904</v>
       </c>
-      <c r="F65" s="20">
+      <c r="F65" s="17">
         <f t="shared" si="18"/>
         <v>7920</v>
       </c>
-      <c r="G65" s="19">
+      <c r="G65" s="16">
         <f t="shared" si="19"/>
         <v>23645.983745336904</v>
       </c>
-      <c r="H65" s="19">
+      <c r="H65" s="16">
         <f t="shared" si="20"/>
         <v>2799.9074805692508</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66" s="21">
+      <c r="A66" s="18">
         <v>10</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="13">
         <f t="shared" si="14"/>
         <v>509.52187334891573</v>
       </c>
-      <c r="C66" s="16">
+      <c r="C66" s="13">
         <f t="shared" si="15"/>
         <v>509.52187334891573</v>
       </c>
-      <c r="D66" s="16">
+      <c r="D66" s="13">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E66" s="19">
+      <c r="E66" s="16">
         <f t="shared" si="17"/>
         <v>17691.731713504018</v>
       </c>
-      <c r="F66" s="20">
+      <c r="F66" s="17">
         <f t="shared" si="18"/>
         <v>8800</v>
       </c>
-      <c r="G66" s="19">
+      <c r="G66" s="16">
         <f t="shared" si="19"/>
         <v>26491.731713504018</v>
       </c>
-      <c r="H66" s="19">
+      <c r="H66" s="16">
         <f t="shared" si="20"/>
         <v>2845.7479681671139</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67" s="21">
+      <c r="A67" s="18">
         <v>11</v>
       </c>
-      <c r="B67" s="16">
+      <c r="B67" s="13">
         <f t="shared" si="14"/>
         <v>567.47998644235474</v>
       </c>
-      <c r="C67" s="16">
+      <c r="C67" s="13">
         <f t="shared" si="15"/>
         <v>567.47998644235474</v>
       </c>
-      <c r="D67" s="16">
+      <c r="D67" s="13">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E67" s="19">
+      <c r="E67" s="16">
         <f t="shared" si="17"/>
         <v>19704.166195915095</v>
       </c>
-      <c r="F67" s="20">
+      <c r="F67" s="17">
         <f t="shared" si="18"/>
         <v>9680</v>
       </c>
-      <c r="G67" s="19">
+      <c r="G67" s="16">
         <f t="shared" si="19"/>
         <v>29384.166195915095</v>
       </c>
-      <c r="H67" s="19">
+      <c r="H67" s="16">
         <f t="shared" si="20"/>
         <v>2892.4344824110776</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68" s="21">
+      <c r="A68" s="18">
         <v>12</v>
       </c>
-      <c r="B68" s="16">
+      <c r="B68" s="13">
         <f t="shared" si="14"/>
         <v>626.80743957041921</v>
       </c>
-      <c r="C68" s="16">
+      <c r="C68" s="13">
         <f t="shared" si="15"/>
         <v>626.80743957041921</v>
       </c>
-      <c r="D68" s="16">
+      <c r="D68" s="13">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E68" s="19">
+      <c r="E68" s="16">
         <f t="shared" si="17"/>
         <v>21764.147207306221</v>
       </c>
-      <c r="F68" s="20">
+      <c r="F68" s="17">
         <f t="shared" si="18"/>
         <v>10560</v>
       </c>
-      <c r="G68" s="19">
+      <c r="G68" s="16">
         <f t="shared" si="19"/>
         <v>32324.147207306221</v>
       </c>
-      <c r="H68" s="19">
+      <c r="H68" s="16">
         <f t="shared" si="20"/>
         <v>2939.9810113911262</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69" s="21">
+      <c r="A69" s="18">
         <v>13</v>
       </c>
-      <c r="B69" s="16">
+      <c r="B69" s="13">
         <f t="shared" si="14"/>
         <v>687.52941027880343</v>
       </c>
-      <c r="C69" s="16">
+      <c r="C69" s="13">
         <f t="shared" si="15"/>
         <v>687.52941027880343</v>
       </c>
-      <c r="D69" s="16">
+      <c r="D69" s="13">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E69" s="19">
+      <c r="E69" s="16">
         <f t="shared" si="17"/>
         <v>23872.548968014009</v>
       </c>
-      <c r="F69" s="20">
+      <c r="F69" s="17">
         <f t="shared" si="18"/>
         <v>11440</v>
       </c>
-      <c r="G69" s="19">
+      <c r="G69" s="16">
         <f t="shared" si="19"/>
         <v>35312.548968014009</v>
       </c>
-      <c r="H69" s="19">
+      <c r="H69" s="16">
         <f t="shared" si="20"/>
         <v>2988.4017607077876</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70" s="21">
+      <c r="A70" s="18">
         <v>14</v>
       </c>
-      <c r="B70" s="16">
+      <c r="B70" s="13">
         <f t="shared" si="14"/>
         <v>749.67149159246469</v>
       </c>
-      <c r="C70" s="16">
+      <c r="C70" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D70" s="16">
+      <c r="D70" s="13">
         <f t="shared" si="16"/>
         <v>29.67149159246469</v>
       </c>
-      <c r="E70" s="19">
+      <c r="E70" s="16">
         <f t="shared" si="17"/>
         <v>25515.130062369179</v>
       </c>
-      <c r="F70" s="20">
+      <c r="F70" s="17">
         <f t="shared" si="18"/>
         <v>12320</v>
       </c>
-      <c r="G70" s="19">
+      <c r="G70" s="16">
         <f t="shared" si="19"/>
         <v>37835.130062369179</v>
       </c>
-      <c r="H70" s="19">
+      <c r="H70" s="16">
         <f t="shared" si="20"/>
         <v>2522.5810943551696</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" s="21">
+      <c r="A71" s="18">
         <v>15</v>
       </c>
-      <c r="B71" s="16">
+      <c r="B71" s="13">
         <f t="shared" si="14"/>
         <v>813.25969846861108</v>
       </c>
-      <c r="C71" s="16">
+      <c r="C71" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D71" s="16">
+      <c r="D71" s="13">
         <f t="shared" si="16"/>
         <v>93.259698468611077</v>
       </c>
-      <c r="E71" s="19">
+      <c r="E71" s="16">
         <f t="shared" si="17"/>
         <v>26619.091987302276</v>
       </c>
-      <c r="F71" s="20">
+      <c r="F71" s="17">
         <f t="shared" si="18"/>
         <v>13200</v>
       </c>
-      <c r="G71" s="19">
+      <c r="G71" s="16">
         <f t="shared" si="19"/>
         <v>39819.091987302279</v>
       </c>
-      <c r="H71" s="19">
+      <c r="H71" s="16">
         <f t="shared" si="20"/>
         <v>1983.9619249331008</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72" s="21">
+      <c r="A72" s="18">
         <v>16</v>
       </c>
-      <c r="B72" s="16">
+      <c r="B72" s="13">
         <f t="shared" si="14"/>
         <v>878.32047434610013</v>
       </c>
-      <c r="C72" s="16">
+      <c r="C72" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D72" s="16">
+      <c r="D72" s="13">
         <f t="shared" si="16"/>
         <v>158.32047434610013</v>
       </c>
-      <c r="E72" s="19">
+      <c r="E72" s="16">
         <f t="shared" si="17"/>
         <v>27748.619346286461</v>
       </c>
-      <c r="F72" s="20">
+      <c r="F72" s="17">
         <f t="shared" si="18"/>
         <v>14080</v>
       </c>
-      <c r="G72" s="19">
+      <c r="G72" s="16">
         <f t="shared" si="19"/>
         <v>41828.619346286461</v>
       </c>
-      <c r="H72" s="19">
+      <c r="H72" s="16">
         <f t="shared" si="20"/>
         <v>2009.5273589841818</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" s="21">
+      <c r="A73" s="18">
         <v>17</v>
       </c>
-      <c r="B73" s="16">
+      <c r="B73" s="13">
         <f t="shared" si="14"/>
         <v>944.88069779264049</v>
       </c>
-      <c r="C73" s="16">
+      <c r="C73" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D73" s="16">
+      <c r="D73" s="13">
         <f t="shared" si="16"/>
         <v>224.88069779264049</v>
       </c>
-      <c r="E73" s="19">
+      <c r="E73" s="16">
         <f t="shared" si="17"/>
         <v>28904.178781122231</v>
       </c>
-      <c r="F73" s="20">
+      <c r="F73" s="17">
         <f t="shared" si="18"/>
         <v>14960</v>
       </c>
-      <c r="G73" s="19">
+      <c r="G73" s="16">
         <f t="shared" si="19"/>
         <v>43864.178781122231</v>
       </c>
-      <c r="H73" s="19">
+      <c r="H73" s="16">
         <f t="shared" si="20"/>
         <v>2035.5594348357699</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74" s="21">
+      <c r="A74" s="18">
         <v>18</v>
       </c>
-      <c r="B74" s="16">
+      <c r="B74" s="13">
         <f t="shared" si="14"/>
         <v>1012.9676892512279</v>
       </c>
-      <c r="C74" s="16">
+      <c r="C74" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D74" s="16">
+      <c r="D74" s="13">
         <f t="shared" si="16"/>
         <v>292.96768925122785</v>
       </c>
-      <c r="E74" s="19">
+      <c r="E74" s="16">
         <f t="shared" si="17"/>
         <v>30086.244605056039</v>
       </c>
-      <c r="F74" s="20">
+      <c r="F74" s="17">
         <f t="shared" si="18"/>
         <v>15840</v>
       </c>
-      <c r="G74" s="19">
+      <c r="G74" s="16">
         <f t="shared" si="19"/>
         <v>45926.244605056039</v>
       </c>
-      <c r="H74" s="19">
+      <c r="H74" s="16">
         <f t="shared" si="20"/>
         <v>2062.0658239338081</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75" s="21">
+      <c r="A75" s="18">
         <v>19</v>
       </c>
-      <c r="B75" s="16">
+      <c r="B75" s="13">
         <f t="shared" si="14"/>
         <v>1082.6092178872495</v>
       </c>
-      <c r="C75" s="16">
+      <c r="C75" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D75" s="16">
+      <c r="D75" s="13">
         <f t="shared" si="16"/>
         <v>362.60921788724954</v>
       </c>
-      <c r="E75" s="19">
+      <c r="E75" s="16">
         <f t="shared" si="17"/>
         <v>31295.298921653637</v>
       </c>
-      <c r="F75" s="20">
+      <c r="F75" s="17">
         <f t="shared" si="18"/>
         <v>16720</v>
       </c>
-      <c r="G75" s="19">
+      <c r="G75" s="16">
         <f t="shared" si="19"/>
         <v>48015.298921653637</v>
       </c>
-      <c r="H75" s="19">
+      <c r="H75" s="16">
         <f t="shared" si="20"/>
         <v>2089.0543165975978</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76" s="21">
+      <c r="A76" s="18">
         <v>20</v>
       </c>
-      <c r="B76" s="16">
+      <c r="B76" s="13">
         <f t="shared" si="14"/>
         <v>1153.8335085377266</v>
       </c>
-      <c r="C76" s="16">
+      <c r="C76" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D76" s="16">
+      <c r="D76" s="13">
         <f t="shared" si="16"/>
         <v>433.83350853772663</v>
       </c>
-      <c r="E76" s="19">
+      <c r="E76" s="16">
         <f t="shared" si="17"/>
         <v>32531.831745446641</v>
       </c>
-      <c r="F76" s="20">
+      <c r="F76" s="17">
         <f t="shared" si="18"/>
         <v>17600</v>
       </c>
-      <c r="G76" s="19">
+      <c r="G76" s="16">
         <f t="shared" si="19"/>
         <v>50131.831745446645</v>
       </c>
-      <c r="H76" s="19">
+      <c r="H76" s="16">
         <f t="shared" si="20"/>
         <v>2116.532823793008</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77" s="21">
+      <c r="A77" s="18">
         <v>21</v>
       </c>
-      <c r="B77" s="16">
+      <c r="B77" s="13">
         <f t="shared" si="14"/>
         <v>1226.6692487641703</v>
       </c>
-      <c r="C77" s="16">
+      <c r="C77" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D77" s="16">
+      <c r="D77" s="13">
         <f t="shared" si="16"/>
         <v>506.66924876417033</v>
       </c>
-      <c r="E77" s="19">
+      <c r="E77" s="16">
         <f t="shared" si="17"/>
         <v>33796.341124377956</v>
       </c>
-      <c r="F77" s="20">
+      <c r="F77" s="17">
         <f t="shared" si="18"/>
         <v>18480</v>
       </c>
-      <c r="G77" s="19">
+      <c r="G77" s="16">
         <f t="shared" si="19"/>
         <v>52276.341124377956</v>
       </c>
-      <c r="H77" s="19">
+      <c r="H77" s="16">
         <f t="shared" si="20"/>
         <v>2144.5093789313105</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78" s="21">
+      <c r="A78" s="18">
         <v>22</v>
       </c>
-      <c r="B78" s="16">
+      <c r="B78" s="13">
         <f t="shared" si="14"/>
         <v>1301.1455960105666</v>
       </c>
-      <c r="C78" s="16">
+      <c r="C78" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D78" s="16">
+      <c r="D78" s="13">
         <f t="shared" si="16"/>
         <v>581.14559601056658</v>
       </c>
-      <c r="E78" s="19">
+      <c r="E78" s="16">
         <f t="shared" si="17"/>
         <v>35089.333264072338</v>
       </c>
-      <c r="F78" s="20">
+      <c r="F78" s="17">
         <f t="shared" si="18"/>
         <v>19360</v>
       </c>
-      <c r="G78" s="19">
+      <c r="G78" s="16">
         <f t="shared" si="19"/>
         <v>54449.333264072338</v>
       </c>
-      <c r="H78" s="19">
+      <c r="H78" s="16">
         <f t="shared" si="20"/>
         <v>2172.9921396943828</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79" s="21">
+      <c r="A79" s="18">
         <v>23</v>
       </c>
-      <c r="B79" s="16">
+      <c r="B79" s="13">
         <f t="shared" si="14"/>
         <v>1377.292184868003</v>
       </c>
-      <c r="C79" s="16">
+      <c r="C79" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D79" s="16">
+      <c r="D79" s="13">
         <f t="shared" si="16"/>
         <v>657.29218486800301</v>
       </c>
-      <c r="E79" s="19">
+      <c r="E79" s="16">
         <f t="shared" si="17"/>
         <v>36411.322653958385</v>
       </c>
-      <c r="F79" s="20">
+      <c r="F79" s="17">
         <f t="shared" si="18"/>
         <v>20240</v>
       </c>
-      <c r="G79" s="19">
+      <c r="G79" s="16">
         <f t="shared" si="19"/>
         <v>56651.322653958385</v>
       </c>
-      <c r="H79" s="19">
+      <c r="H79" s="16">
         <f t="shared" si="20"/>
         <v>2201.9893898860464</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A80" s="21">
+      <c r="A80" s="18">
         <v>24</v>
       </c>
-      <c r="B80" s="16">
+      <c r="B80" s="13">
         <f t="shared" si="14"/>
         <v>1455.1391344474989</v>
       </c>
-      <c r="C80" s="16">
+      <c r="C80" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D80" s="16">
+      <c r="D80" s="13">
         <f t="shared" si="16"/>
         <v>735.13913444749892</v>
       </c>
-      <c r="E80" s="19">
+      <c r="E80" s="16">
         <f t="shared" si="17"/>
         <v>37762.832195269075</v>
       </c>
-      <c r="F80" s="20">
+      <c r="F80" s="17">
         <f t="shared" si="18"/>
         <v>21120</v>
       </c>
-      <c r="G80" s="19">
+      <c r="G80" s="16">
         <f t="shared" si="19"/>
         <v>58882.832195269075</v>
       </c>
-      <c r="H80" s="19">
+      <c r="H80" s="16">
         <f t="shared" si="20"/>
         <v>2231.5095413106901</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="21">
+      <c r="A81" s="18">
         <v>25</v>
       </c>
-      <c r="B81" s="16">
+      <c r="B81" s="13">
         <f t="shared" si="14"/>
         <v>1534.7170558625965</v>
       </c>
-      <c r="C81" s="16">
+      <c r="C81" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D81" s="16">
+      <c r="D81" s="13">
         <f t="shared" si="16"/>
         <v>814.71705586259645</v>
       </c>
-      <c r="E81" s="19">
+      <c r="E81" s="16">
         <f t="shared" si="17"/>
         <v>39144.393330947853</v>
       </c>
-      <c r="F81" s="20">
+      <c r="F81" s="17">
         <f t="shared" si="18"/>
         <v>22000</v>
       </c>
-      <c r="G81" s="19">
+      <c r="G81" s="16">
         <f t="shared" si="19"/>
         <v>61144.393330947853</v>
       </c>
-      <c r="H81" s="19">
+      <c r="H81" s="16">
         <f t="shared" si="20"/>
         <v>2261.5611356787776</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="21">
+      <c r="A82" s="18">
         <v>26</v>
       </c>
-      <c r="B82" s="16">
+      <c r="B82" s="13">
         <f t="shared" si="14"/>
         <v>1616.0570598233144</v>
       </c>
-      <c r="C82" s="16">
+      <c r="C82" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D82" s="16">
+      <c r="D82" s="13">
         <f t="shared" si="16"/>
         <v>896.05705982331438</v>
       </c>
-      <c r="E82" s="19">
+      <c r="E82" s="16">
         <f t="shared" si="17"/>
         <v>40556.546177488097</v>
       </c>
-      <c r="F82" s="20">
+      <c r="F82" s="17">
         <f t="shared" si="18"/>
         <v>22880</v>
       </c>
-      <c r="G82" s="19">
+      <c r="G82" s="16">
         <f t="shared" si="19"/>
         <v>63436.546177488097</v>
       </c>
-      <c r="H82" s="19">
+      <c r="H82" s="16">
         <f t="shared" si="20"/>
         <v>2292.1528465402444</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" s="21">
+      <c r="A83" s="18">
         <v>27</v>
       </c>
-      <c r="B83" s="16">
+      <c r="B83" s="13">
         <f t="shared" si="14"/>
         <v>1699.1907643430709</v>
       </c>
-      <c r="C83" s="16">
+      <c r="C83" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D83" s="16">
+      <c r="D83" s="13">
         <f t="shared" si="16"/>
         <v>979.1907643430709</v>
       </c>
-      <c r="E83" s="19">
+      <c r="E83" s="16">
         <f t="shared" si="17"/>
         <v>41999.839658733865</v>
       </c>
-      <c r="F83" s="20">
+      <c r="F83" s="17">
         <f t="shared" si="18"/>
         <v>23760</v>
       </c>
-      <c r="G83" s="19">
+      <c r="G83" s="16">
         <f t="shared" si="19"/>
         <v>65759.839658733865</v>
       </c>
-      <c r="H83" s="19">
+      <c r="H83" s="16">
         <f t="shared" si="20"/>
         <v>2323.2934812457679</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84" s="21">
+      <c r="A84" s="18">
         <v>28</v>
       </c>
-      <c r="B84" s="16">
+      <c r="B84" s="13">
         <f t="shared" si="14"/>
         <v>1784.1503025602246</v>
       </c>
-      <c r="C84" s="16">
+      <c r="C84" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D84" s="16">
+      <c r="D84" s="13">
         <f t="shared" si="16"/>
         <v>1064.1503025602246</v>
       </c>
-      <c r="E84" s="19">
+      <c r="E84" s="16">
         <f t="shared" si="17"/>
         <v>43474.831641670564</v>
       </c>
-      <c r="F84" s="20">
+      <c r="F84" s="17">
         <f t="shared" si="18"/>
         <v>24640</v>
       </c>
-      <c r="G84" s="19">
+      <c r="G84" s="16">
         <f t="shared" si="19"/>
         <v>68114.831641670564</v>
       </c>
-      <c r="H84" s="19">
+      <c r="H84" s="16">
         <f t="shared" si="20"/>
         <v>2354.9919829366991</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" s="21">
+      <c r="A85" s="18">
         <v>29</v>
       </c>
-      <c r="B85" s="16">
+      <c r="B85" s="13">
         <f t="shared" si="14"/>
         <v>1870.9683306758782</v>
       </c>
-      <c r="C85" s="16">
+      <c r="C85" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D85" s="16">
+      <c r="D85" s="13">
         <f t="shared" si="16"/>
         <v>1150.9683306758782</v>
       </c>
-      <c r="E85" s="19">
+      <c r="E85" s="16">
         <f t="shared" si="17"/>
         <v>44982.089074233998</v>
       </c>
-      <c r="F85" s="20">
+      <c r="F85" s="17">
         <f t="shared" si="18"/>
         <v>25520</v>
       </c>
-      <c r="G85" s="19">
+      <c r="G85" s="16">
         <f t="shared" si="19"/>
         <v>70502.089074233998</v>
       </c>
-      <c r="H85" s="19">
+      <c r="H85" s="16">
         <f t="shared" si="20"/>
         <v>2387.2574325634341</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A86" s="21">
+      <c r="A86" s="18">
         <v>30</v>
       </c>
-      <c r="B86" s="16">
+      <c r="B86" s="13">
         <f t="shared" si="14"/>
         <v>1959.6780360096488</v>
       </c>
-      <c r="C86" s="16">
+      <c r="C86" s="13">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="D86" s="16">
+      <c r="D86" s="13">
         <f t="shared" si="16"/>
         <v>1239.6780360096488</v>
       </c>
-      <c r="E86" s="19">
+      <c r="E86" s="16">
         <f t="shared" si="17"/>
         <v>46522.188125167515</v>
       </c>
-      <c r="F86" s="20">
+      <c r="F86" s="17">
         <f t="shared" si="18"/>
         <v>26400</v>
       </c>
-      <c r="G86" s="19">
+      <c r="G86" s="16">
         <f t="shared" si="19"/>
         <v>72922.188125167508</v>
       </c>
-      <c r="H86" s="19">
+      <c r="H86" s="16">
         <f t="shared" si="20"/>
         <v>2420.0990509335097</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" s="23" t="s">
+      <c r="A87" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B87" s="24">
+      <c r="B87" s="20">
         <f>MES_PRICE</f>
         <v>2700</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
+      <c r="D87" s="29"/>
+      <c r="E87" s="29"/>
+      <c r="F87" s="29"/>
+      <c r="G87" s="29"/>
+      <c r="H87" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4389,6 +7092,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4403,26 +7107,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="21">
         <f>1*TOM_HRS_PER_BED*WEEKS*(1+TOM_DIM_RET)^1</f>
         <v>99.000000000000014</v>
       </c>
@@ -4440,12 +7144,12 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -4456,7 +7160,7 @@
       <c r="A9" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="1" t="s">
         <v>113</v>
       </c>
     </row>
@@ -4464,7 +7168,7 @@
       <c r="A10" t="s">
         <v>114</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="1" t="s">
         <v>115</v>
       </c>
     </row>
@@ -4472,64 +7176,64 @@
       <c r="A11" t="s">
         <v>116</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="1" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22" t="s">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="2" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="1" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="1" t="s">
         <v>124</v>
       </c>
     </row>
@@ -4537,29 +7241,29 @@
       <c r="A17" t="s">
         <v>126</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="1" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="4" t="s">
         <v>132</v>
       </c>
     </row>
@@ -4567,10 +7271,10 @@
       <c r="A21" t="s">
         <v>133</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="22">
         <v>10</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="23">
         <f>OPT_TOM_BEDS</f>
         <v>10</v>
       </c>
@@ -4583,10 +7287,10 @@
       <c r="A22" t="s">
         <v>134</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="22">
         <v>20</v>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="23">
         <f>OPT_CAR_BEDS</f>
         <v>20</v>
       </c>
@@ -4599,10 +7303,10 @@
       <c r="A23" t="s">
         <v>135</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="22">
         <v>30</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="23">
         <f>OPT_MES_BEDS</f>
         <v>30</v>
       </c>
@@ -4615,10 +7319,10 @@
       <c r="A24" t="s">
         <v>136</v>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="24">
         <v>42762</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="25">
         <f>PROFIT</f>
         <v>42761.664682745002</v>
       </c>
@@ -4628,41 +7332,41 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="2" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasmindeguzman/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasmindeguzman/Library/Mobile Documents/com~apple~CloudDocs/1 UH MBA/620 Micro and Macro Economoics/GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBF9695-0E21-9F44-93CA-6D681CA3393F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAEA7254-428F-8D4D-A510-441B9C1B62EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32440" yWindow="-5440" windowWidth="29260" windowHeight="19900" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5040" yWindow="660" windowWidth="23140" windowHeight="18460" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -962,6 +962,64 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="rnd">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>'Marginal-Cost Schedules'!$J$7:$J$8</c:f>
@@ -1672,6 +1730,64 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="rnd">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>'Marginal-Cost Schedules'!$J$31:$J$32</c:f>
@@ -2253,6 +2369,834 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Mesclun Marginal Cost vs. Market Price</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Mesclun Price</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:tint val="50000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="35000">
+                    <a:schemeClr val="accent1">
+                      <a:tint val="37000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:tint val="15000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="1"/>
+                <a:tileRect/>
+              </a:gradFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:shade val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="rnd">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Marginal-Cost Schedules'!$J$56:$J$57</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Marginal-Cost Schedules'!$K$56:$K$57</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2700</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FD7A-434C-BFF6-12CA2F633672}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Marginal Cost</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:tint val="50000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="35000">
+                    <a:schemeClr val="accent2">
+                      <a:tint val="37000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:tint val="15000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="1"/>
+                <a:tileRect/>
+              </a:gradFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:shade val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Marginal-Cost Schedules'!$A$56:$A$86</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Marginal-Cost Schedules'!$H$56:$H$86</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0.00</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="1">
+                  <c:v>2462.03125</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2501.58203125</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2541.8743896484366</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2582.920684814454</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2624.7334694862348</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2667.3254924178127</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2710.7097013180683</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2754.8992458326466</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2799.9074805692508</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2845.7479681671139</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2892.4344824110776</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2939.9810113911262</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2988.4017607077876</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2522.5810943551696</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1983.9619249331008</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2009.5273589841818</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2035.5594348357699</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2062.0658239338081</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2089.0543165975978</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2116.532823793008</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2144.5093789313105</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2172.9921396943828</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2201.9893898860464</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2231.5095413106901</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2261.5611356787776</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2292.1528465402444</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2323.2934812457679</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2354.9919829366991</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2387.2574325634341</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2420.0990509335097</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FD7A-434C-BFF6-12CA2F633672}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="172224767"/>
+        <c:axId val="170598719"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="172224767"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Mesclun Beds</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="170598719"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="170598719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" b="1"/>
+                  <a:t>Marginal Cost ($)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="172224767"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:alpha val="0"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2294,6 +3238,46 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3435,20 +4419,571 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="246">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="70000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" spc="0" baseline="0"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="95000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1">
+              <a:alpha val="0"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" spc="0" baseline="0"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>374650</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:colOff>577850</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
+      <xdr:colOff>527050</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3504,6 +5039,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1B72FEB-4235-8701-5C21-C2B908C88CD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5888,7 +7459,7 @@
         <v>1670.9013431626554</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="18">
         <v>18</v>
       </c>
@@ -5921,7 +7492,7 @@
         <v>1589.1387909931072</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="18">
         <v>19</v>
       </c>
@@ -5954,7 +7525,7 @@
         <v>1638.1753169880685</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="18">
         <v>20</v>
       </c>
@@ -5987,7 +7558,7 @@
         <v>1688.9454575384007</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="19" t="s">
         <v>101</v>
       </c>
@@ -6004,7 +7575,7 @@
       <c r="G52" s="29"/>
       <c r="H52" s="29"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="30" t="s">
         <v>104</v>
       </c>
@@ -6016,7 +7587,7 @@
       <c r="G54" s="30"/>
       <c r="H54" s="30"/>
     </row>
-    <row r="55" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" ht="30" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>93</v>
       </c>
@@ -6042,7 +7613,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="18">
         <v>0</v>
       </c>
@@ -6071,8 +7642,14 @@
         <v>0</v>
       </c>
       <c r="H56" s="18"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="K56">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="18">
         <v>1</v>
       </c>
@@ -6104,8 +7681,14 @@
         <f t="shared" ref="H57:H86" si="20">G57-G56</f>
         <v>2462.03125</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J57">
+        <v>30</v>
+      </c>
+      <c r="K57">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="18">
         <v>2</v>
       </c>
@@ -6138,7 +7721,7 @@
         <v>2501.58203125</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="18">
         <v>3</v>
       </c>
@@ -6171,7 +7754,7 @@
         <v>2541.8743896484366</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="18">
         <v>4</v>
       </c>
@@ -6204,7 +7787,7 @@
         <v>2582.920684814454</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="18">
         <v>5</v>
       </c>
@@ -6237,7 +7820,7 @@
         <v>2624.7334694862348</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="18">
         <v>6</v>
       </c>
@@ -6270,7 +7853,7 @@
         <v>2667.3254924178127</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="18">
         <v>7</v>
       </c>
@@ -6303,7 +7886,7 @@
         <v>2710.7097013180683</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="18">
         <v>8</v>
       </c>
